--- a/public/sap-reporting/expansion-150-downloads/EXT-MM23-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM23-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R51acf183c0054a25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rc19df91b70cf4786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R47f9e90e081d4b9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3bd1c6b79dd4482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R9f9b0e91dfd44dae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R26b3d5efee2f46cd"/>
   </x:sheets>
 </x:workbook>
 </file>
